--- a/Encollect_Web_DBS_P1/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/Encollect_Web_DBS_P1/Cypress/fixtures/AgencyTemplate.xlsx
@@ -401,61 +401,61 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Kevin</v>
+        <v>Aleen</v>
       </c>
       <c r="B2" t="str">
-        <v>Kutch</v>
+        <v>Ondricka</v>
       </c>
       <c r="C2" t="str">
-        <v>QY9EGT</v>
+        <v>IVZMP1</v>
       </c>
       <c r="D2" t="str">
-        <v>Jennyfer83@gmail.com</v>
+        <v>Brielle67@gmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>pkfRig2X</v>
+        <v>mFIIbe8X</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-08-14</v>
+        <v>2025-05-27</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-01-10</v>
+        <v>2025-06-14</v>
       </c>
       <c r="H2" t="str">
-        <v>PbBHAbwcgl</v>
+        <v>TX9WAERPbx</v>
       </c>
       <c r="I2" t="str">
-        <v>Sports</v>
+        <v>Beauty</v>
       </c>
       <c r="J2" t="str">
-        <v>Principal Configuration Technician</v>
+        <v>Human Group Facilitator</v>
       </c>
       <c r="K2" t="str">
-        <v>2025-01-06</v>
+        <v>2025-04-30</v>
       </c>
       <c r="L2" t="str">
-        <v>2473484189</v>
+        <v>9417494892</v>
       </c>
       <c r="M2" t="str">
-        <v>Jared_Cassin@hotmail.com</v>
+        <v>Marian_Langosh66@gmail.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Reina</v>
+        <v>Bennie</v>
       </c>
       <c r="O2" t="str">
-        <v>47632 Feil Ranch</v>
+        <v>72864 State Street</v>
       </c>
       <c r="P2" t="str">
-        <v>07112</v>
+        <v>59592</v>
       </c>
       <c r="Q2" t="str">
-        <v>2025-03-19</v>
+        <v>2026-02-02</v>
       </c>
       <c r="R2" t="str">
-        <v>2025-03-31</v>
+        <v>2026-02-01</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-09-05</v>
+        <v>2026-02-24</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_DBS_P1/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/Encollect_Web_DBS_P1/Cypress/fixtures/AgencyTemplate.xlsx
@@ -401,61 +401,61 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Aleen</v>
+        <v>Marilyne</v>
       </c>
       <c r="B2" t="str">
-        <v>Ondricka</v>
+        <v>Heidenreich</v>
       </c>
       <c r="C2" t="str">
-        <v>IVZMP1</v>
+        <v>SVTUZK</v>
       </c>
       <c r="D2" t="str">
-        <v>Brielle67@gmail.com</v>
+        <v>Connie.Grady-Huel5@yahoo.com</v>
       </c>
       <c r="E2" t="str">
-        <v>mFIIbe8X</v>
+        <v>ha4Wjdca</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-05-27</v>
+        <v>2025-12-14</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-06-14</v>
+        <v>2025-08-01</v>
       </c>
       <c r="H2" t="str">
-        <v>TX9WAERPbx</v>
+        <v>GFqH1zZPC4</v>
       </c>
       <c r="I2" t="str">
-        <v>Beauty</v>
+        <v>Grocery</v>
       </c>
       <c r="J2" t="str">
-        <v>Human Group Facilitator</v>
+        <v>International Operations Consultant</v>
       </c>
       <c r="K2" t="str">
-        <v>2025-04-30</v>
+        <v>2025-06-26</v>
       </c>
       <c r="L2" t="str">
-        <v>9417494892</v>
+        <v>8518198354</v>
       </c>
       <c r="M2" t="str">
-        <v>Marian_Langosh66@gmail.com</v>
+        <v>Kris38@hotmail.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Bennie</v>
+        <v>Chauncey</v>
       </c>
       <c r="O2" t="str">
-        <v>72864 State Street</v>
+        <v>10071 Ebert Meadow</v>
       </c>
       <c r="P2" t="str">
-        <v>59592</v>
+        <v>54400</v>
       </c>
       <c r="Q2" t="str">
-        <v>2026-02-02</v>
+        <v>2025-09-26</v>
       </c>
       <c r="R2" t="str">
-        <v>2026-02-01</v>
+        <v>2025-07-25</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-05-10</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_DBS_P1/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/Encollect_Web_DBS_P1/Cypress/fixtures/AgencyTemplate.xlsx
@@ -401,61 +401,61 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="str">
-        <v>Marilyne</v>
+        <v>Cyril</v>
       </c>
       <c r="B2" t="str">
-        <v>Heidenreich</v>
+        <v>Grimes</v>
       </c>
       <c r="C2" t="str">
-        <v>SVTUZK</v>
+        <v>UUEKH7</v>
       </c>
       <c r="D2" t="str">
-        <v>Connie.Grady-Huel5@yahoo.com</v>
+        <v>Leora_Willms@gmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>ha4Wjdca</v>
+        <v>gRXcXPh5</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-12-14</v>
+        <v>2026-06-11</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-08-01</v>
+        <v>2025-08-07</v>
       </c>
       <c r="H2" t="str">
-        <v>GFqH1zZPC4</v>
+        <v>IcaFwMo5BL</v>
       </c>
       <c r="I2" t="str">
-        <v>Grocery</v>
+        <v>Electronics</v>
       </c>
       <c r="J2" t="str">
-        <v>International Operations Consultant</v>
+        <v>District Accounts Officer</v>
       </c>
       <c r="K2" t="str">
-        <v>2025-06-26</v>
+        <v>2025-07-20</v>
       </c>
       <c r="L2" t="str">
-        <v>8518198354</v>
+        <v>9291231949</v>
       </c>
       <c r="M2" t="str">
-        <v>Kris38@hotmail.com</v>
+        <v>Zita11@hotmail.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Chauncey</v>
+        <v>Santos</v>
       </c>
       <c r="O2" t="str">
-        <v>10071 Ebert Meadow</v>
+        <v>44851 8th Street</v>
       </c>
       <c r="P2" t="str">
-        <v>54400</v>
+        <v>53675-0585</v>
       </c>
       <c r="Q2" t="str">
-        <v>2025-09-26</v>
+        <v>2026-06-14</v>
       </c>
       <c r="R2" t="str">
-        <v>2025-07-25</v>
+        <v>2026-02-19</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-05-10</v>
+        <v>2027-05-28</v>
       </c>
     </row>
   </sheetData>
